--- a/backend/app/Assets/templates/gpb_template.xlsx
+++ b/backend/app/Assets/templates/gpb_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\GAD_AMS_2\backend\app\Assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2727F7F-CB70-4BE4-B586-5D6213F98F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DFDE22-0373-4FDF-ABB0-8A56C99C04AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -380,7 +380,7 @@
     </r>
   </si>
   <si>
-    <t>ANNUAL GENDER AND DEVELOPMENT (GAD) PLAN AND BUDGET FY 2026</t>
+    <t>ANNUAL GENDER AND DEVELOPMENT (GAD) PLAN AND BUDGET</t>
   </si>
 </sst>
 </file>
@@ -668,15 +668,198 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -694,189 +877,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1203,147 +1203,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
     </row>
     <row r="2" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="78" t="s">
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="80"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="44"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="80"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="44"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="25"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="48"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="36"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="23" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="48"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="36"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="23" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="48"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="36"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="30"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="48"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="36"/>
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1352,14 +1352,14 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="65"/>
-      <c r="M8" s="65"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
@@ -1369,29 +1369,29 @@
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="68" t="s">
+      <c r="D9" s="50"/>
+      <c r="E9" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="43" t="s">
+      <c r="F9" s="52"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="45"/>
+      <c r="I9" s="55"/>
       <c r="J9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="71" t="s">
+      <c r="L9" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="M9" s="72"/>
+      <c r="M9" s="57"/>
       <c r="N9" s="10" t="s">
         <v>15</v>
       </c>
@@ -1405,29 +1405,29 @@
       <c r="B10" s="12">
         <v>1</v>
       </c>
-      <c r="C10" s="73">
+      <c r="C10" s="58">
         <v>2</v>
       </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="73">
+      <c r="D10" s="59"/>
+      <c r="E10" s="58">
         <v>3</v>
       </c>
-      <c r="F10" s="75"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="73">
+      <c r="F10" s="60"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="58">
         <v>4</v>
       </c>
-      <c r="I10" s="74"/>
+      <c r="I10" s="59"/>
       <c r="J10" s="12">
         <v>5</v>
       </c>
       <c r="K10" s="12">
         <v>6</v>
       </c>
-      <c r="L10" s="73">
+      <c r="L10" s="58">
         <v>7</v>
       </c>
-      <c r="M10" s="74"/>
+      <c r="M10" s="59"/>
       <c r="N10" s="12">
         <v>8</v>
       </c>
@@ -1437,163 +1437,163 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="64"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="47"/>
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="35"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="79"/>
       <c r="J12" s="15"/>
       <c r="K12" s="14"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="33"/>
+      <c r="L12" s="76"/>
+      <c r="M12" s="77"/>
       <c r="N12" s="14"/>
       <c r="O12" s="14"/>
       <c r="P12" s="11"/>
     </row>
     <row r="13" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="51"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="69"/>
     </row>
     <row r="14" spans="1:16" ht="270" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="20"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="58"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="82"/>
       <c r="J14" s="18"/>
       <c r="K14" s="20"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="61"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="85"/>
       <c r="N14" s="17"/>
       <c r="O14" s="20"/>
     </row>
     <row r="15" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="51"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="69"/>
     </row>
     <row r="16" spans="1:16" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="22"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="53"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="71"/>
       <c r="J16" s="18"/>
       <c r="K16" s="22"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="56"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="74"/>
       <c r="N16" s="19"/>
       <c r="O16" s="17"/>
     </row>
     <row r="17" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="41"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="66"/>
       <c r="N17" s="21"/>
       <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" ht="24.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="41"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="66"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:15" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1602,104 +1602,93 @@
       <c r="O19" s="1"/>
     </row>
     <row r="20" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="43" t="s">
+      <c r="A20" s="54"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="44"/>
-      <c r="O20" s="45"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="55"/>
     </row>
     <row r="21" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="46"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="48"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="36"/>
     </row>
     <row r="22" spans="1:15" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="28"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="86"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="87"/>
+      <c r="N22" s="88"/>
+      <c r="O22" s="89"/>
     </row>
     <row r="23" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="31"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:O4"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="M22:O23"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="A13:O13"/>
     <mergeCell ref="M20:O20"/>
     <mergeCell ref="A21:O21"/>
     <mergeCell ref="A17:K17"/>
@@ -1714,22 +1703,33 @@
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="G20:L20"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="M22:O23"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:O6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
